--- a/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.Audit.Source.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.Audit.Source.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.3</t>
+    <t>4.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-31T14:38:46-05:00</t>
+    <t>2026-06-15T14:55:16-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.Audit.Source.xlsx
+++ b/ITI/MHD/StructureDefinition-IHE.MHD.SimplifiedPublish.Audit.Source.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>4.2.4</t>
+    <t>4.2.5-comment</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T14:55:16-05:00</t>
+    <t>2026-06-16T19:25:56-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
